--- a/Ejercicios/23.- CDS.xlsx
+++ b/Ejercicios/23.- CDS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Trabajos Iteso\6to Semestre\Administración de Riesgos\Administracion_de_Riesgos\Ejercicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B6EE0C-DB52-49EE-8167-97C0B8C82293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A03F9B7-33DF-4688-B107-AA7E179FE600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{223C4D70-38E2-CB4A-94D3-A5B58E3B486D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{223C4D70-38E2-CB4A-94D3-A5B58E3B486D}"/>
   </bookViews>
   <sheets>
     <sheet name="Teoría" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="86">
   <si>
     <t>CDS: Credit Default Swaps.</t>
   </si>
@@ -166,9 +166,6 @@
     <t>Y solo el comprador desembolsa la prima spread sobre la posición.</t>
   </si>
   <si>
-    <t>b) Responde, si sucede un evento de crédito, ¿Cuánto % de la posición total tiene que pagar el Protection Seller?</t>
-  </si>
-  <si>
     <t xml:space="preserve">EJERCICIO 2. </t>
   </si>
   <si>
@@ -223,9 +220,6 @@
     <t>A 3 años sobre la deuda en el screenshot, asumir un LGD del 57%</t>
   </si>
   <si>
-    <t>c) Asume que el CDS se cierra sobre 2,000,000 bonos, si HOY sucede un evento de crédito, ¿Cuánto $ de la posición total tiene que pagar el PS?</t>
-  </si>
-  <si>
     <t>Calculate the bond’s YTM, yield to first call, yield to second call, and yield to worst.</t>
   </si>
   <si>
@@ -278,18 +272,76 @@
   </si>
   <si>
     <t>YTW</t>
+  </si>
+  <si>
+    <t>a) Calculo de la prima del CDS</t>
+  </si>
+  <si>
+    <t>Settle</t>
+  </si>
+  <si>
+    <t>Maturity</t>
+  </si>
+  <si>
+    <t>RR</t>
+  </si>
+  <si>
+    <t>LGD</t>
+  </si>
+  <si>
+    <t>Spread Crediticio</t>
+  </si>
+  <si>
+    <t>rf 2026</t>
+  </si>
+  <si>
+    <t>***** Tomar la tasa libre de riesgo del bono</t>
+  </si>
+  <si>
+    <t>Porque estoy calculando el spread crediticio</t>
+  </si>
+  <si>
+    <t>que está pagando el bono y no el CDS</t>
+  </si>
+  <si>
+    <t>prob default</t>
+  </si>
+  <si>
+    <t>Prima Spread</t>
+  </si>
+  <si>
+    <t>puntos base</t>
+  </si>
+  <si>
+    <t>b) Despues de calcular la cprima spread, ¿Cuánto tendrá que desembolsar el PB periodicamente)</t>
+  </si>
+  <si>
+    <t>c) Responde, si sucede un evento de crédito, ¿Cuánto % de la posición total tiene que pagar el Protection Seller?</t>
+  </si>
+  <si>
+    <t>d) Asume que el CDS se cierra sobre 2,000,000 bonos, si HOY sucede un evento de crédito, ¿Cuánto $ de la posición total tiene que pagar el PS?</t>
+  </si>
+  <si>
+    <t>b)</t>
+  </si>
+  <si>
+    <t>c)</t>
+  </si>
+  <si>
+    <t>d)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000%"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
-    <numFmt numFmtId="172" formatCode="0.0000"/>
-    <numFmt numFmtId="174" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -395,12 +447,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -437,24 +490,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="3" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -1366,14 +1418,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>294640</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>132080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>660400</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>190480</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>190479</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1410,13 +1462,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>397430</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>185889</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>620401</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>133453</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1466,6 +1518,116 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
+          <a:endParaRPr lang="es-MX" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>60476</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>24190</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>448128</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>53621</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="CuadroTexto 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19D4EE3E-9B7D-4AE0-8AEF-10ECB15E54B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12706047" y="223761"/>
+          <a:ext cx="2945795" cy="1408289"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100"/>
+            <a:t>Tasa de</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100" baseline="0"/>
+            <a:t> recuperación (Recovery Rate)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100" baseline="0"/>
+            <a:t>- Deuda Senior: 40%</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100" baseline="0"/>
+            <a:t>- Deuda Junior o SUB: 20% </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-MX" sz="1100" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100" baseline="0"/>
+            <a:t>Spread de Credito: YTW - rf </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100" baseline="0"/>
+            <a:t>LGD = 1- Recovery Rate</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-MX" sz="1100" baseline="0"/>
+            <a:t>Prob Default: spread de crédito/LGD</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
           <a:endParaRPr lang="es-MX" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -2186,7 +2348,7 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
@@ -2194,7 +2356,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
@@ -2227,7 +2389,7 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
@@ -2289,7 +2451,7 @@
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.3">
@@ -2304,7 +2466,7 @@
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.3">
@@ -2346,72 +2508,72 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D8" s="12"/>
       <c r="G8" s="19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" s="20">
         <v>0.06</v>
       </c>
       <c r="D9" s="12"/>
-      <c r="F9" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="24">
+      <c r="F9" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="14">
         <v>2.6352715089414992E-2</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="14">
         <f>+G9*2</f>
         <v>5.2705430178829983E-2</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B10" s="17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C10" s="21">
         <v>6</v>
       </c>
       <c r="D10" s="12"/>
-      <c r="F10" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="24">
+      <c r="F10" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="14">
         <v>2.9411775498112632E-2</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="24">
         <f>+G10*2</f>
         <v>5.8823550996225264E-2</v>
       </c>
@@ -2419,7 +2581,7 @@
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D11" s="12"/>
       <c r="F11" s="19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G11" s="15">
         <v>2.7058046210496213E-2</v>
@@ -2431,16 +2593,16 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B12" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G12" s="14">
         <f>+MIN(G9:G11)</f>
@@ -2459,7 +2621,7 @@
         <f>+$C$9/2*100</f>
         <v>3</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="23">
         <f>+C13/(1+$G$10)^B13</f>
         <v>2.9142856837326905</v>
       </c>
@@ -2472,14 +2634,14 @@
         <f>+$C$9/2*100+102</f>
         <v>105</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="23">
         <f>+C14/(1+$G$10)^B14</f>
         <v>99.08571220810866</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C16" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D16" s="22">
         <f>+SUM(D13:D14)</f>
@@ -2493,109 +2655,200 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD5C187-66F5-6B47-A36E-CEFFAD85D891}">
-  <dimension ref="B1:L36"/>
+  <dimension ref="B1:Q37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.296875" customWidth="1"/>
+    <col min="12" max="12" width="13.09765625" customWidth="1"/>
+    <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="L12" s="9"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="L13" s="9"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="L14" s="9"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="L15" s="9"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="L13" s="25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="L14" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14" s="26">
+        <v>45775</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="L15" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" s="26">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="L16" s="9"/>
     </row>
-    <row r="17" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L17" s="9"/>
-    </row>
-    <row r="18" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L18" s="9"/>
-    </row>
-    <row r="19" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="12:17" x14ac:dyDescent="0.3">
+      <c r="L17" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="M17" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="O17" t="s">
+        <v>72</v>
+      </c>
+      <c r="P17" s="5">
+        <f>+P18-P19</f>
+        <v>1.0353000000000001E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="12:17" x14ac:dyDescent="0.3">
+      <c r="L18" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="M18" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="O18" t="s">
+        <v>66</v>
+      </c>
+      <c r="P18" s="5">
+        <v>4.9599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="12:17" x14ac:dyDescent="0.3">
       <c r="L19" s="9"/>
-    </row>
-    <row r="20" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="O19" t="s">
+        <v>73</v>
+      </c>
+      <c r="P19" s="27">
+        <v>3.9246999999999997E-2</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="12:17" x14ac:dyDescent="0.3">
       <c r="L20" s="9"/>
-    </row>
-    <row r="21" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="Q20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="12:17" x14ac:dyDescent="0.3">
       <c r="L21" s="9"/>
-    </row>
-    <row r="22" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L22" s="9"/>
-    </row>
-    <row r="23" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="Q21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="12:17" x14ac:dyDescent="0.3">
+      <c r="L22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22" s="12">
+        <f>+P17/M18</f>
+        <v>1.7255000000000003E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="12:17" x14ac:dyDescent="0.3">
       <c r="L23" s="9"/>
     </row>
-    <row r="24" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L24" s="9"/>
-    </row>
-    <row r="25" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="12:17" x14ac:dyDescent="0.3">
+      <c r="L24" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="M24">
+        <v>105.1713</v>
+      </c>
+      <c r="N24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="12:17" x14ac:dyDescent="0.3">
       <c r="L25" s="9"/>
-    </row>
-    <row r="26" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="M25" s="12">
+        <f>+M24/10000</f>
+        <v>1.051713E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="12:17" x14ac:dyDescent="0.3">
       <c r="L26" s="9"/>
     </row>
-    <row r="27" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="12:17" x14ac:dyDescent="0.3">
       <c r="L27" s="9"/>
     </row>
-    <row r="28" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L28" s="9"/>
-    </row>
-    <row r="29" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="12:17" x14ac:dyDescent="0.3">
+      <c r="L28" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="M28" s="28">
+        <f>+M25*100*2000000</f>
+        <v>2103426</v>
+      </c>
+    </row>
+    <row r="29" spans="12:17" x14ac:dyDescent="0.3">
       <c r="L29" s="9"/>
     </row>
-    <row r="30" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L30" s="9"/>
-    </row>
-    <row r="31" spans="12:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="12:17" x14ac:dyDescent="0.3">
+      <c r="L30" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="M30" s="4">
+        <f>+M18</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="31" spans="12:17" x14ac:dyDescent="0.3">
       <c r="L31" s="9"/>
     </row>
-    <row r="32" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L32" s="9"/>
+    <row r="32" spans="12:17" x14ac:dyDescent="0.3">
+      <c r="L32" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="M32" s="28">
+        <f>+M30*2000000*100</f>
+        <v>120000000</v>
+      </c>
     </row>
     <row r="33" spans="12:12" x14ac:dyDescent="0.3">
       <c r="L33" s="9"/>
@@ -2608,6 +2861,9 @@
     </row>
     <row r="36" spans="12:12" x14ac:dyDescent="0.3">
       <c r="L36" s="9"/>
+    </row>
+    <row r="37" spans="12:12" x14ac:dyDescent="0.3">
+      <c r="L37" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2627,12 +2883,12 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
@@ -2681,17 +2937,17 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2710,32 +2966,32 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B1" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
